--- a/data/gravel/Cinelli King Zydeco 2 2025.xlsx
+++ b/data/gravel/Cinelli King Zydeco 2 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{478399CF-66D5-B642-BACD-654EA665347A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14382F7D-9AA3-AF4A-9CAF-1741211024E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2840" yWindow="500" windowWidth="25960" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data/gravel/Cinelli King Zydeco 2 2025.xlsx
+++ b/data/gravel/Cinelli King Zydeco 2 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14382F7D-9AA3-AF4A-9CAF-1741211024E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{257C614C-7639-0248-A1C1-D585333BDF8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2840" yWindow="500" windowWidth="25960" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="107">
   <si>
     <t>brand</t>
   </si>
@@ -351,6 +351,9 @@
   </si>
   <si>
     <t>a8:g34</t>
+  </si>
+  <si>
+    <t>https://usa.cinelli-milano.com/cdn/shop/files/KING_ZYDECO2_white_frameset_1800x1800.jpg?v=1737435998</t>
   </si>
 </sst>
 </file>
@@ -759,6 +762,11 @@
         <v>84</v>
       </c>
     </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>106</v>
+      </c>
+    </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>5</v>

--- a/data/gravel/Cinelli King Zydeco 2 2025.xlsx
+++ b/data/gravel/Cinelli King Zydeco 2 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{257C614C-7639-0248-A1C1-D585333BDF8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{991D678E-7ADD-1C4B-ADF4-407B5C130D17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2840" yWindow="500" windowWidth="25960" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="109">
   <si>
     <t>brand</t>
   </si>
@@ -344,9 +344,6 @@
     <t>top_tube_actual_length</t>
   </si>
   <si>
-    <t>usd</t>
-  </si>
-  <si>
     <t>braze on</t>
   </si>
   <si>
@@ -354,6 +351,15 @@
   </si>
   <si>
     <t>https://usa.cinelli-milano.com/cdn/shop/files/KING_ZYDECO2_white_frameset_1800x1800.jpg?v=1737435998</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Milan, Italy</t>
+  </si>
+  <si>
+    <t>USD</t>
   </si>
 </sst>
 </file>
@@ -716,7 +722,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J74"/>
+  <dimension ref="A1:J75"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -764,7 +770,7 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
@@ -772,7 +778,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
@@ -1736,7 +1742,7 @@
         <v>45</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C54" s="1"/>
       <c r="D54" s="1"/>
@@ -2026,7 +2032,7 @@
         <v>65</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C74" s="1"/>
       <c r="D74" s="1"/>
@@ -2037,6 +2043,14 @@
       <c r="I74" s="1"/>
       <c r="J74" s="1"/>
     </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>106</v>
+      </c>
+      <c r="B75" t="s">
+        <v>107</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/gravel/Cinelli King Zydeco 2 2025.xlsx
+++ b/data/gravel/Cinelli King Zydeco 2 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{991D678E-7ADD-1C4B-ADF4-407B5C130D17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F903F6D6-D1D8-C84E-BDE9-92D01FC5F35F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2840" yWindow="500" windowWidth="25960" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="115">
   <si>
     <t>brand</t>
   </si>
@@ -360,6 +360,24 @@
   </si>
   <si>
     <t>USD</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -722,7 +740,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J75"/>
+  <dimension ref="A1:J81"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1695,11 +1713,9 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>88</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="B51" s="1"/>
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
@@ -1711,7 +1727,7 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>43</v>
+        <v>110</v>
       </c>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -1725,7 +1741,7 @@
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>44</v>
+        <v>111</v>
       </c>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
@@ -1739,11 +1755,9 @@
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>103</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="B54" s="1"/>
       <c r="C54" s="1"/>
       <c r="D54" s="1"/>
       <c r="E54" s="1"/>
@@ -1755,7 +1769,7 @@
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>46</v>
+        <v>113</v>
       </c>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -1769,7 +1783,7 @@
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>47</v>
+        <v>114</v>
       </c>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
@@ -1783,10 +1797,10 @@
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B57" s="1">
-        <v>160</v>
+        <v>42</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>88</v>
       </c>
       <c r="C57" s="1"/>
       <c r="D57" s="1"/>
@@ -1799,11 +1813,9 @@
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B58" s="1">
-        <v>160</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="B58" s="1"/>
       <c r="C58" s="1"/>
       <c r="D58" s="1"/>
       <c r="E58" s="1"/>
@@ -1815,7 +1827,7 @@
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
@@ -1829,9 +1841,11 @@
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B60" s="1"/>
+        <v>45</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>103</v>
+      </c>
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
@@ -1843,7 +1857,7 @@
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
@@ -1857,7 +1871,7 @@
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
@@ -1871,9 +1885,11 @@
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B63" s="1"/>
+        <v>48</v>
+      </c>
+      <c r="B63" s="1">
+        <v>160</v>
+      </c>
       <c r="C63" s="1"/>
       <c r="D63" s="1"/>
       <c r="E63" s="1"/>
@@ -1885,9 +1901,11 @@
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B64" s="1"/>
+        <v>49</v>
+      </c>
+      <c r="B64" s="1">
+        <v>160</v>
+      </c>
       <c r="C64" s="1"/>
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
@@ -1899,7 +1917,7 @@
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
@@ -1913,7 +1931,7 @@
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
@@ -1927,7 +1945,7 @@
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
@@ -1941,7 +1959,7 @@
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
@@ -1955,7 +1973,7 @@
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
@@ -1969,7 +1987,7 @@
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
@@ -1983,11 +2001,9 @@
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B71" s="1">
-        <v>3990</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="B71" s="1"/>
       <c r="C71" s="1"/>
       <c r="D71" s="1"/>
       <c r="E71" s="1"/>
@@ -1999,11 +2015,9 @@
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B72" s="1">
-        <v>5490</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="B72" s="1"/>
       <c r="C72" s="1"/>
       <c r="D72" s="1"/>
       <c r="E72" s="1"/>
@@ -2015,7 +2029,7 @@
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
@@ -2029,11 +2043,9 @@
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>108</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="B74" s="1"/>
       <c r="C74" s="1"/>
       <c r="D74" s="1"/>
       <c r="E74" s="1"/>
@@ -2044,10 +2056,100 @@
       <c r="J74" s="1"/>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
+      <c r="A75" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B75" s="1"/>
+      <c r="C75" s="1"/>
+      <c r="D75" s="1"/>
+      <c r="E75" s="1"/>
+      <c r="F75" s="1"/>
+      <c r="G75" s="1"/>
+      <c r="H75" s="1"/>
+      <c r="I75" s="1"/>
+      <c r="J75" s="1"/>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A76" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B76" s="1"/>
+      <c r="C76" s="1"/>
+      <c r="D76" s="1"/>
+      <c r="E76" s="1"/>
+      <c r="F76" s="1"/>
+      <c r="G76" s="1"/>
+      <c r="H76" s="1"/>
+      <c r="I76" s="1"/>
+      <c r="J76" s="1"/>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A77" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B77" s="1">
+        <v>3990</v>
+      </c>
+      <c r="C77" s="1"/>
+      <c r="D77" s="1"/>
+      <c r="E77" s="1"/>
+      <c r="F77" s="1"/>
+      <c r="G77" s="1"/>
+      <c r="H77" s="1"/>
+      <c r="I77" s="1"/>
+      <c r="J77" s="1"/>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A78" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B78" s="1">
+        <v>5490</v>
+      </c>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="1"/>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A79" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B79" s="1"/>
+      <c r="C79" s="1"/>
+      <c r="D79" s="1"/>
+      <c r="E79" s="1"/>
+      <c r="F79" s="1"/>
+      <c r="G79" s="1"/>
+      <c r="H79" s="1"/>
+      <c r="I79" s="1"/>
+      <c r="J79" s="1"/>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A80" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C80" s="1"/>
+      <c r="D80" s="1"/>
+      <c r="E80" s="1"/>
+      <c r="F80" s="1"/>
+      <c r="G80" s="1"/>
+      <c r="H80" s="1"/>
+      <c r="I80" s="1"/>
+      <c r="J80" s="1"/>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
         <v>106</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B81" t="s">
         <v>107</v>
       </c>
     </row>

--- a/data/gravel/Cinelli King Zydeco 2 2025.xlsx
+++ b/data/gravel/Cinelli King Zydeco 2 2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F903F6D6-D1D8-C84E-BDE9-92D01FC5F35F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89C55B04-8205-054C-8347-1AED388AFFD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2840" yWindow="500" windowWidth="25960" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3700" yWindow="500" windowWidth="25960" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1403,24 +1403,19 @@
       </c>
       <c r="B33" s="1"/>
       <c r="C33" s="1">
-        <f>C35</f>
         <v>156</v>
       </c>
       <c r="D33" s="1">
-        <f>AVERAGE(D35,C36)</f>
-        <v>165.5</v>
+        <v>166</v>
       </c>
       <c r="E33" s="1">
-        <f t="shared" ref="E33:G33" si="0">AVERAGE(E35,D36)</f>
-        <v>171.5</v>
+        <v>172</v>
       </c>
       <c r="F33" s="1">
-        <f t="shared" si="0"/>
-        <v>178.5</v>
+        <v>179</v>
       </c>
       <c r="G33" s="1">
-        <f t="shared" si="0"/>
-        <v>186.5</v>
+        <v>187</v>
       </c>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
@@ -1432,23 +1427,18 @@
       </c>
       <c r="B34" s="1"/>
       <c r="C34" s="1">
-        <f>D33</f>
-        <v>165.5</v>
+        <v>165</v>
       </c>
       <c r="D34" s="1">
-        <f t="shared" ref="D34:F34" si="1">E33</f>
-        <v>171.5</v>
+        <v>171</v>
       </c>
       <c r="E34" s="1">
-        <f t="shared" si="1"/>
-        <v>178.5</v>
+        <v>178</v>
       </c>
       <c r="F34" s="1">
-        <f t="shared" si="1"/>
-        <v>186.5</v>
+        <v>186</v>
       </c>
       <c r="G34" s="1">
-        <f>G36</f>
         <v>193</v>
       </c>
       <c r="H34" s="1"/>
@@ -1458,21 +1448,6 @@
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
-      <c r="C35" s="1">
-        <v>156</v>
-      </c>
-      <c r="D35" s="1">
-        <v>166</v>
-      </c>
-      <c r="E35" s="1">
-        <v>172</v>
-      </c>
-      <c r="F35" s="1">
-        <v>179</v>
-      </c>
-      <c r="G35" s="1">
-        <v>187</v>
-      </c>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
@@ -1483,21 +1458,6 @@
       </c>
       <c r="B36" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="C36" s="1">
-        <v>165</v>
-      </c>
-      <c r="D36" s="1">
-        <v>171</v>
-      </c>
-      <c r="E36" s="1">
-        <v>178</v>
-      </c>
-      <c r="F36" s="1">
-        <v>186</v>
-      </c>
-      <c r="G36" s="1">
-        <v>193</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
